--- a/artfynd/A 16539-2024 artfynd.xlsx
+++ b/artfynd/A 16539-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121430302</v>
       </c>
       <c r="B2" t="n">
-        <v>108965</v>
+        <v>108978</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 16539-2024 artfynd.xlsx
+++ b/artfynd/A 16539-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121430302</v>
       </c>
       <c r="B2" t="n">
-        <v>108978</v>
+        <v>108979</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 16539-2024 artfynd.xlsx
+++ b/artfynd/A 16539-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121430302</v>
       </c>
       <c r="B2" t="n">
-        <v>108979</v>
+        <v>108982</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -770,7 +770,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anna-Lotta Hellqvist, Lisa Stridh, Emma Karlsson</t>
+          <t>Emma Karlsson, Lisa Stridh, Anna-Lotta Hellqvist</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>

--- a/artfynd/A 16539-2024 artfynd.xlsx
+++ b/artfynd/A 16539-2024 artfynd.xlsx
@@ -770,7 +770,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Emma Karlsson, Lisa Stridh, Anna-Lotta Hellqvist</t>
+          <t>Anna-Lotta Hellqvist, Lisa Stridh, Emma Karlsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>

--- a/artfynd/A 16539-2024 artfynd.xlsx
+++ b/artfynd/A 16539-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121430302</v>
       </c>
       <c r="B2" t="n">
-        <v>108982</v>
+        <v>108988</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 16539-2024 artfynd.xlsx
+++ b/artfynd/A 16539-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121430302</v>
       </c>
       <c r="B2" t="n">
-        <v>108988</v>
+        <v>108989</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 16539-2024 artfynd.xlsx
+++ b/artfynd/A 16539-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121430302</v>
       </c>
       <c r="B2" t="n">
-        <v>108989</v>
+        <v>108997</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
